--- a/history_matching/example/iter1/Cuts/RadiusShouldBe15/train_data.xlsx
+++ b/history_matching/example/iter1/Cuts/RadiusShouldBe15/train_data.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -67,100 +68,136 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20170712_102507.000000</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000001</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000002</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000003</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000004</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000005</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000006</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000007</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000008</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000009</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000010</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000011</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000012</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000013</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000014</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000015</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000016</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000017</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000018</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000019</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000020</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000021</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000022</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000023</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000024</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000025</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000026</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000027</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000028</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000029</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000030</t>
+    <t>Data_20180119_074303.000000</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000001</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000002</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000003</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000004</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000005</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000006</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000007</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000008</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000009</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000010</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000011</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000012</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000013</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000014</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000015</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000016</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000017</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000018</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000019</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000020</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000021</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000022</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000023</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000024</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000025</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000026</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000027</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000028</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000029</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000030</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000031</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000032</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000033</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000034</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000035</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000036</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000037</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000038</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000039</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000040</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000041</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000042</t>
   </si>
 </sst>
 </file>
@@ -509,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -576,46 +613,46 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-18.04118948177776</v>
+        <v>2.186099688264044</v>
       </c>
       <c r="E2" t="n">
-        <v>-11.64358846342563</v>
+        <v>-2.139445702561019</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>23.94865099677753</v>
+        <v>2.145783012867295</v>
       </c>
       <c r="H2" t="n">
-        <v>20.37952019948665</v>
+        <v>7.253615269822205</v>
       </c>
       <c r="I2" t="n">
-        <v>3.569130797290882</v>
+        <v>-5.107832256954911</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004628267895632038</v>
+        <v>-4.490691390535565e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>20.38414846738228</v>
+        <v>7.253615224915292</v>
       </c>
       <c r="L2" t="n">
-        <v>2.945606398135232</v>
+        <v>3.933822174127515</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09169325232505798</v>
+        <v>1.0207237312335e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>2.362103404366394</v>
+        <v>3.115089788428652</v>
       </c>
       <c r="O2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.076880792950678</v>
+        <v>-2.575308496071165</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.77145735711014</v>
+        <v>-15987.57212125578</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -629,46 +666,46 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.824148924904549</v>
+        <v>24.07984869323391</v>
       </c>
       <c r="E3" t="n">
-        <v>-16.24289861220373</v>
+        <v>-11.58956938733648</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>16.82869086366553</v>
+        <v>26.24499798705829</v>
       </c>
       <c r="H3" t="n">
-        <v>15.94833124522822</v>
+        <v>27.11285241181588</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8803596184373106</v>
+        <v>-0.8678544247575886</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.002257331599657673</v>
+        <v>6.862175237448274e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>15.94607391362856</v>
+        <v>27.11285241867806</v>
       </c>
       <c r="L3" t="n">
-        <v>2.935216641168569</v>
+        <v>3.93382217412754</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08130349963903427</v>
+        <v>1.020723978858604e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4154718603657559</v>
+        <v>4.870997758790599</v>
       </c>
       <c r="O3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5151719196579811</v>
+        <v>-0.4375619241821689</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.09540619211281</v>
+        <v>-2716.393776706067</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -682,46 +719,46 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5685187880030469</v>
+        <v>-9.016405488666004</v>
       </c>
       <c r="E4" t="n">
-        <v>-17.79115785323854</v>
+        <v>-4.823317184306902</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>17.21073956844748</v>
+        <v>11.3297339723723</v>
       </c>
       <c r="H4" t="n">
-        <v>17.46317720211567</v>
+        <v>10.33520508073548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2524376336681939</v>
+        <v>0.994528891636822</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.001823726171093423</v>
+        <v>1.272892722626377e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>17.46135347594458</v>
+        <v>10.3352050934644</v>
       </c>
       <c r="L4" t="n">
-        <v>2.935755147175207</v>
+        <v>3.933822174127514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08184200525283813</v>
+        <v>1.020723716993224e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.080856363622885</v>
+        <v>1.875875702069566</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1462666290347837</v>
+        <v>0.5014296799723392</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.876026075052589</v>
+        <v>3112.886568908816</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -735,46 +772,46 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.057121594267954</v>
+        <v>4.859916288097089</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.504572336221827</v>
+        <v>-31.32942135452733</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>9.263062716667703</v>
+        <v>33.60200418543344</v>
       </c>
       <c r="H5" t="n">
-        <v>9.969490100939538</v>
+        <v>32.94924213567299</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7064273842718354</v>
+        <v>0.6527620497604474</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0001062161881872133</v>
+        <v>-4.395897507043858e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.96938388475135</v>
+        <v>32.94924209171401</v>
       </c>
       <c r="L5" t="n">
-        <v>2.929522929767721</v>
+        <v>3.933822174127522</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07560978829860687</v>
+        <v>1.020723808826089e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.210427615450605</v>
+        <v>7.218012321021144</v>
       </c>
       <c r="O5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4126708297481617</v>
+        <v>0.3291149153066654</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.568698887765558</v>
+        <v>2043.152598099124</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -788,46 +825,46 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-13.35251836315878</v>
+        <v>-16.02079393798419</v>
       </c>
       <c r="E6" t="n">
-        <v>15.78123281001729</v>
+        <v>-18.75135171052559</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>20.98672650836765</v>
+        <v>23.61158847221721</v>
       </c>
       <c r="H6" t="n">
-        <v>18.8088158266753</v>
+        <v>24.04360947279838</v>
       </c>
       <c r="I6" t="n">
-        <v>2.177910681692349</v>
+        <v>-0.4320210005811695</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002587248719715924</v>
+        <v>3.982084798009562e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>18.81140307539502</v>
+        <v>24.04360951261923</v>
       </c>
       <c r="L6" t="n">
-        <v>2.939920811720234</v>
+        <v>3.933822174127523</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08600766956806183</v>
+        <v>1.0207238190164e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.673033027017172</v>
+        <v>3.636748813963774</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.268691475679476</v>
+        <v>-0.2178198910301953</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.417460462971685</v>
+        <v>-1352.230644545</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -841,46 +878,46 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>16.55353419180717</v>
+        <v>-22.21519901616071</v>
       </c>
       <c r="E7" t="n">
-        <v>10.86653090602863</v>
+        <v>19.67113524689151</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>21.70851647633481</v>
+        <v>30.05940074136868</v>
       </c>
       <c r="H7" t="n">
-        <v>19.64670597629117</v>
+        <v>32.06741893873789</v>
       </c>
       <c r="I7" t="n">
-        <v>2.061810500043638</v>
+        <v>-2.008018197369207</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.006084016450593767</v>
+        <v>4.064277691757568e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>19.64062195984058</v>
+        <v>32.06741897938066</v>
       </c>
       <c r="L7" t="n">
-        <v>2.952390408060033</v>
+        <v>3.933822174127537</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09847726672887802</v>
+        <v>1.020723943734916e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>2.034579764045656</v>
+        <v>6.863400685763197</v>
       </c>
       <c r="O7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.203487236448366</v>
+        <v>-1.01241900946168</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.58962010450001</v>
+        <v>-6285.118955854149</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -894,46 +931,46 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.96271503522054</v>
+        <v>14.71013225950182</v>
       </c>
       <c r="E8" t="n">
-        <v>5.913511551678141</v>
+        <v>-26.57688483605933</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>6.201568913875604</v>
+        <v>30.62284658747639</v>
       </c>
       <c r="H8" t="n">
-        <v>9.003074054299873</v>
+        <v>31.45755939714243</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.801505140424269</v>
+        <v>-0.8347128096660441</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.003105628103742099</v>
+        <v>-2.592072776555766e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.99996842619613</v>
+        <v>31.45755937122171</v>
       </c>
       <c r="L8" t="n">
-        <v>2.930165353165852</v>
+        <v>3.933822174127529</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07625220715999603</v>
+        <v>1.020723867154073e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.636220448047665</v>
+        <v>6.618155001110223</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.634796322229358</v>
+        <v>-0.4208522979059683</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.13406135659634</v>
+        <v>-2612.660202632832</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -947,46 +984,46 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-16.53731150211988</v>
+        <v>-13.50780455188965</v>
       </c>
       <c r="E9" t="n">
-        <v>-18.64175006945499</v>
+        <v>-23.35173533077449</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>22.9240927552754</v>
+        <v>26.93047520653213</v>
       </c>
       <c r="H9" t="n">
-        <v>25.72645110900851</v>
+        <v>26.73266078823161</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.802358353733108</v>
+        <v>0.197814418300517</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004141829344538144</v>
+        <v>3.257013686277855e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>25.73059293835304</v>
+        <v>26.73266082080175</v>
       </c>
       <c r="L9" t="n">
-        <v>2.947293039219691</v>
+        <v>3.933822174127521</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09337989985942841</v>
+        <v>1.02072379858368e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>4.706901588157023</v>
+        <v>4.718109540792438</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.634757790489987</v>
+        <v>0.09973567005880241</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.184137632673231</v>
+        <v>619.1612259089213</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1000,46 +1037,46 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>21.07190327309267</v>
+        <v>23.73451069352058</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.579856232544273</v>
+        <v>5.534927670994279</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>21.27318504755872</v>
+        <v>23.23343656808299</v>
       </c>
       <c r="H10" t="n">
-        <v>22.27769727800174</v>
+        <v>23.48520708255433</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.004512230443019</v>
+        <v>-0.2517705144713354</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.006103155299437374</v>
+        <v>6.169137500765327e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>22.2715941227023</v>
+        <v>23.48520708872346</v>
       </c>
       <c r="L10" t="n">
-        <v>2.963166258859146</v>
+        <v>3.933822174127539</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1092531159520149</v>
+        <v>1.020723976927631e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.184775635426371</v>
+        <v>3.412195846480628</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5800033607501776</v>
+        <v>-0.1269397141386713</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.020588899015244</v>
+        <v>-788.0444590186383</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1053,46 +1090,46 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.920101219265611</v>
+        <v>-24.53380220870584</v>
       </c>
       <c r="E11" t="n">
-        <v>4.725526362327059</v>
+        <v>12.12810024526132</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>4.956646536978488</v>
+        <v>29.40932511489485</v>
       </c>
       <c r="H11" t="n">
-        <v>8.433721036285021</v>
+        <v>29.2787070458993</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.477074499306534</v>
+        <v>0.1306180689955525</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.002757558631872514</v>
+        <v>3.649417922412153e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>8.430963477653149</v>
+        <v>29.27870708239347</v>
       </c>
       <c r="L11" t="n">
-        <v>2.929261791937468</v>
+        <v>3.93382217412754</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07534864544868469</v>
+        <v>1.020723984266272e-07</v>
       </c>
       <c r="N11" t="n">
-        <v>2.886474629871549</v>
+        <v>5.74196298218885</v>
       </c>
       <c r="O11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.029973369085745</v>
+        <v>0.06585606474062591</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12.65702641244593</v>
+        <v>408.8358562740019</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1106,46 +1143,46 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>12.75674007460906</v>
+        <v>2.314465242766595</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.815619801961887</v>
+        <v>8.694287936571882</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>16.99760439380548</v>
+        <v>9.325313624883758</v>
       </c>
       <c r="H12" t="n">
-        <v>14.91555458048674</v>
+        <v>8.889661883643612</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08204981331874</v>
+        <v>0.4356517412401466</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.005170027456076857</v>
+        <v>-4.554943435388997e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91038455303067</v>
+        <v>8.889661838094177</v>
       </c>
       <c r="L12" t="n">
-        <v>2.944686057044765</v>
+        <v>3.933822174127517</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09077291190624237</v>
+        <v>1.020723743143283e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03931906866052361</v>
+        <v>2.457178743976164</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.216322370860384</v>
+        <v>0.2196504703505028</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.927715462635835</v>
+        <v>1363.59497165744</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1159,46 +1196,46 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.249593944633105</v>
+        <v>7.965501321120925</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.37958019574265</v>
+        <v>-3.585598447696029</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>15.87532706620174</v>
+        <v>6.962327857642332</v>
       </c>
       <c r="H13" t="n">
-        <v>15.41873528199946</v>
+        <v>9.047566422641523</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4565917842022795</v>
+        <v>-2.085238564999191</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.000249090354116967</v>
+        <v>-4.874543276671825e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>15.41848619164534</v>
+        <v>9.047566373896091</v>
       </c>
       <c r="L13" t="n">
-        <v>2.933438741185065</v>
+        <v>3.933822174127519</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07952559739351273</v>
+        <v>1.020723770448414e-07</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1838112749603256</v>
+        <v>2.393679857553016</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2667328114576115</v>
+        <v>-1.051352559032076</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.61998680680555</v>
+        <v>-6526.819821839931</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1212,46 +1249,46 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.86458171310274</v>
+        <v>-4.303288666319887</v>
       </c>
       <c r="E14" t="n">
-        <v>1.847808520566005</v>
+        <v>-20.87979074122815</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>20.27134275272189</v>
+        <v>20.61503469974378</v>
       </c>
       <c r="H14" t="n">
-        <v>19.71474151708526</v>
+        <v>18.97251635070643</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5566012356366308</v>
+        <v>1.642518349037353</v>
       </c>
       <c r="J14" t="n">
-        <v>0.005766371391042101</v>
+        <v>-1.393659002237656e-08</v>
       </c>
       <c r="K14" t="n">
-        <v>19.7205078884763</v>
+        <v>18.97251633676984</v>
       </c>
       <c r="L14" t="n">
-        <v>2.950653054503503</v>
+        <v>3.933822174127516</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09673991054296494</v>
+        <v>1.02072374127033e-07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.069949673672315</v>
+        <v>1.597486496518939</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.320672964683444</v>
+        <v>0.8281383020261091</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.771000152116676</v>
+        <v>5141.100875922568</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1265,46 +1302,46 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.571714476901889</v>
+        <v>-8.9394739177012</v>
       </c>
       <c r="E15" t="n">
-        <v>24.17223276508321</v>
+        <v>33.20049266139981</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>23.21361779150942</v>
+        <v>35.30718275687315</v>
       </c>
       <c r="H15" t="n">
-        <v>25.3103167614637</v>
+        <v>37.26659892430052</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.096698969954275</v>
+        <v>-1.959416167427371</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0004883136484437286</v>
+        <v>1.053708997859153e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>25.30982844781525</v>
+        <v>37.26659893483762</v>
       </c>
       <c r="L15" t="n">
-        <v>2.939738921940376</v>
+        <v>3.933822174127522</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08582577854394913</v>
+        <v>1.020723804752123e-07</v>
       </c>
       <c r="N15" t="n">
-        <v>4.525626237328374</v>
+        <v>8.954171136456416</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.222589166694113</v>
+        <v>-0.9879144265053926</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.155270238812919</v>
+        <v>-6132.994396080207</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1318,46 +1355,46 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.004526048560841</v>
+        <v>-0.08419433195268056</v>
       </c>
       <c r="E16" t="n">
-        <v>5.15883422605927</v>
+        <v>-30.95110736126681</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>7.818772844355987</v>
+        <v>29.73430230241554</v>
       </c>
       <c r="H16" t="n">
-        <v>9.005822704358479</v>
+        <v>31.69976726845681</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.187049860002492</v>
+        <v>-1.965464966041271</v>
       </c>
       <c r="J16" t="n">
-        <v>1.115814796423217e-05</v>
+        <v>-3.251562860266271e-08</v>
       </c>
       <c r="K16" t="n">
-        <v>9.005833862506444</v>
+        <v>31.69976723594118</v>
       </c>
       <c r="L16" t="n">
-        <v>2.928815526108358</v>
+        <v>3.933822174127521</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07490238547325134</v>
+        <v>1.02072378816159e-07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.633986563693475</v>
+        <v>6.715555177834148</v>
       </c>
       <c r="O16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6936286678954846</v>
+        <v>-0.990964137408311</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.337357337258033</v>
+        <v>-6151.927118153078</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1371,46 +1408,46 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>5.661716124110107</v>
+        <v>19.79603406496537</v>
       </c>
       <c r="E17" t="n">
-        <v>20.47606774644855</v>
+        <v>-6.700193283887272</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>22.53129303438007</v>
+        <v>21.33400885121691</v>
       </c>
       <c r="H17" t="n">
-        <v>21.38585134075208</v>
+        <v>19.27796628346238</v>
       </c>
       <c r="I17" t="n">
-        <v>1.145441693627987</v>
+        <v>2.056042567754535</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.004087315420458977</v>
+        <v>-7.12845748830274e-09</v>
       </c>
       <c r="K17" t="n">
-        <v>21.38176402533162</v>
+        <v>19.27796627633392</v>
       </c>
       <c r="L17" t="n">
-        <v>2.939933901975215</v>
+        <v>3.933822174127532</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08602076023817062</v>
+        <v>1.020723905163169e-07</v>
       </c>
       <c r="N17" t="n">
-        <v>2.801301334166602</v>
+        <v>1.720318503350383</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6704264689606578</v>
+        <v>1.03663231123584</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9193882183549</v>
+        <v>6435.435774923643</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1424,46 +1461,46 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-10.92591156707768</v>
+        <v>-5.111771209066959</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8490017077678118</v>
+        <v>26.44239633506925</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>11.86554327508658</v>
+        <v>26.32306066491322</v>
       </c>
       <c r="H18" t="n">
-        <v>10.44035910227291</v>
+        <v>25.35550078319443</v>
       </c>
       <c r="I18" t="n">
-        <v>1.425184172813672</v>
+        <v>0.9675598817187918</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001970311618312483</v>
+        <v>-1.078177464696814e-08</v>
       </c>
       <c r="K18" t="n">
-        <v>10.44232941389122</v>
+        <v>25.35550077241265</v>
       </c>
       <c r="L18" t="n">
-        <v>2.932205156376827</v>
+        <v>3.933822174127518</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07829201221466064</v>
+        <v>1.020723768637487e-07</v>
       </c>
       <c r="N18" t="n">
-        <v>2.00209938166245</v>
+        <v>4.164305756404272</v>
       </c>
       <c r="O18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8311377117475515</v>
+        <v>0.4878322364890945</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.086410988847224</v>
+        <v>3028.473261724226</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1477,46 +1514,46 @@
         <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.590785578506953</v>
+        <v>-7.980370715859571</v>
       </c>
       <c r="E19" t="n">
-        <v>21.75514286552172</v>
+        <v>0.1087881473155221</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>21.82378786620968</v>
+        <v>8.177566208936263</v>
       </c>
       <c r="H19" t="n">
-        <v>21.82128046927704</v>
+        <v>9.15622519750201</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002507396932639239</v>
+        <v>-0.9786589885657477</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0008049837640049593</v>
+        <v>6.651184586095754e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>21.82047548551304</v>
+        <v>9.156225204153195</v>
       </c>
       <c r="L19" t="n">
-        <v>2.937204986135825</v>
+        <v>3.933822174127513</v>
       </c>
       <c r="M19" t="n">
-        <v>0.08329184353351593</v>
+        <v>1.020723710599904e-07</v>
       </c>
       <c r="N19" t="n">
-        <v>2.994662932445198</v>
+        <v>2.34998437606271</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001932738583763732</v>
+        <v>-0.4934282726033588</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.01147728030807465</v>
+        <v>-3063.213664181071</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1530,46 +1567,46 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>11.55567018211899</v>
+        <v>20.24622118548824</v>
       </c>
       <c r="E20" t="n">
-        <v>3.266395746393158</v>
+        <v>-9.801395121028833</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>12.14950470410536</v>
+        <v>21.15690245477524</v>
       </c>
       <c r="H20" t="n">
-        <v>12.1516057077406</v>
+        <v>21.17896697865268</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.002101003635241128</v>
+        <v>-0.02206452387744307</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.005225283003456887</v>
+        <v>-5.351297029019794e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>12.14638042473714</v>
+        <v>21.17896697330139</v>
       </c>
       <c r="L20" t="n">
-        <v>2.940572125501433</v>
+        <v>3.933822174127533</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08665898442268372</v>
+        <v>1.020723913238547e-07</v>
       </c>
       <c r="N20" t="n">
-        <v>1.252530933744604</v>
+        <v>2.484776767541673</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.001821939463456369</v>
+        <v>-0.01112466887382778</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.01061312025679057</v>
+        <v>-69.06218434023478</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1583,46 +1620,46 @@
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>-30.99786334712302</v>
+        <v>6.748994980594944</v>
       </c>
       <c r="E21" t="n">
-        <v>1.245475460999799</v>
+        <v>-25.20939250478221</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>29.74596566889847</v>
+        <v>27.54423155893729</v>
       </c>
       <c r="H21" t="n">
-        <v>32.47774797457578</v>
+        <v>24.71126723348624</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.731782305677307</v>
+        <v>2.832964325451051</v>
       </c>
       <c r="J21" t="n">
-        <v>0.008023151949779496</v>
+        <v>-4.599692633856438e-08</v>
       </c>
       <c r="K21" t="n">
-        <v>32.48577112652556</v>
+        <v>24.71126718748931</v>
       </c>
       <c r="L21" t="n">
-        <v>2.974150621523396</v>
+        <v>3.933822174127521</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1202374771237373</v>
+        <v>1.020723796599213e-07</v>
       </c>
       <c r="N21" t="n">
-        <v>7.650273200132344</v>
+        <v>3.90523710437807</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.588686653129972</v>
+        <v>1.428347077973344</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.901322647141674</v>
+        <v>8867.209977730949</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1636,46 +1673,46 @@
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>-25.28666245629316</v>
+        <v>-18.64576216183469</v>
       </c>
       <c r="E22" t="n">
-        <v>-10.31378029957536</v>
+        <v>-6.306020405177777</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>28.48358837045081</v>
+        <v>20.15856758020352</v>
       </c>
       <c r="H22" t="n">
-        <v>27.84256636649522</v>
+        <v>18.86887516560614</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6410220039555909</v>
+        <v>1.289692414597379</v>
       </c>
       <c r="J22" t="n">
-        <v>0.006771982800210028</v>
+        <v>4.397906650746034e-08</v>
       </c>
       <c r="K22" t="n">
-        <v>27.84933834929543</v>
+        <v>18.86887520958521</v>
       </c>
       <c r="L22" t="n">
-        <v>2.960710844958911</v>
+        <v>3.933822174127526</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1067977026104927</v>
+        <v>1.020723844603938e-07</v>
       </c>
       <c r="N22" t="n">
-        <v>5.629013344637645</v>
+        <v>1.555808807335141</v>
       </c>
       <c r="O22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3686060788849946</v>
+        <v>0.6502476161094943</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.940794383967843</v>
+        <v>4036.751363091683</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1689,46 +1726,46 @@
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>4.960357405121407</v>
+        <v>27.08979516205517</v>
       </c>
       <c r="E23" t="n">
-        <v>-20.29431573214625</v>
+        <v>-4.277371908924778</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>21.10245222493083</v>
+        <v>27.21659702087382</v>
       </c>
       <c r="H23" t="n">
-        <v>21.07581961290538</v>
+        <v>28.40319585559905</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02663261202545186</v>
+        <v>-1.186598834725231</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.003063137505218635</v>
+        <v>1.313679244110323e-08</v>
       </c>
       <c r="K23" t="n">
-        <v>21.07275647540016</v>
+        <v>28.40319586873584</v>
       </c>
       <c r="L23" t="n">
-        <v>2.940845293805904</v>
+        <v>3.933822174127545</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08693215250968933</v>
+        <v>1.020724031747435e-07</v>
       </c>
       <c r="N23" t="n">
-        <v>2.665427186095215</v>
+        <v>5.389889580143073</v>
       </c>
       <c r="O23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01731642364248578</v>
+        <v>-0.5982690831385115</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1007172961025166</v>
+        <v>-3714.067157848331</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1742,46 +1779,46 @@
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.12895076751893</v>
+        <v>-12.28982422068739</v>
       </c>
       <c r="E24" t="n">
-        <v>12.58552814364026</v>
+        <v>-2.942749773635683</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>13.35169591707897</v>
+        <v>12.6025429531584</v>
       </c>
       <c r="H24" t="n">
-        <v>12.1945009625847</v>
+        <v>12.10057890476043</v>
       </c>
       <c r="I24" t="n">
-        <v>1.157194954494273</v>
+        <v>0.5019640483979746</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.00188296802400609</v>
+        <v>2.916708169968913e-08</v>
       </c>
       <c r="K24" t="n">
-        <v>12.19261799456069</v>
+        <v>12.10057893392751</v>
       </c>
       <c r="L24" t="n">
-        <v>2.930712219665176</v>
+        <v>3.933822174127516</v>
       </c>
       <c r="M24" t="n">
-        <v>0.07679907977581024</v>
+        <v>1.020723741514435e-07</v>
       </c>
       <c r="N24" t="n">
-        <v>1.233408047161351</v>
+        <v>1.165957697367102</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6770582683595018</v>
+        <v>0.2530843124404498</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.182487364133674</v>
+        <v>1571.153003104612</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1795,46 +1832,46 @@
         <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.47176797706838</v>
+        <v>15.44367982075539</v>
       </c>
       <c r="E25" t="n">
-        <v>8.966087380030771</v>
+        <v>-12.56306782461934</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>18.51518991923844</v>
+        <v>18.98484567362867</v>
       </c>
       <c r="H25" t="n">
-        <v>17.19076207097839</v>
+        <v>17.87910137035499</v>
       </c>
       <c r="I25" t="n">
-        <v>1.324427848260047</v>
+        <v>1.105744303273681</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004215261694653378</v>
+        <v>-2.475694622525997e-08</v>
       </c>
       <c r="K25" t="n">
-        <v>17.19497733267305</v>
+        <v>17.87910134559804</v>
       </c>
       <c r="L25" t="n">
-        <v>2.943157264417297</v>
+        <v>3.933822174127527</v>
       </c>
       <c r="M25" t="n">
-        <v>0.08924411982297897</v>
+        <v>1.020723848191226e-07</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9631951839514997</v>
+        <v>1.157786433533515</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7695505173826379</v>
+        <v>0.557503192008339</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.419305712283488</v>
+        <v>3460.99195223197</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1848,46 +1885,46 @@
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.42129338948475</v>
+        <v>13.39850066047773</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.476471144587819</v>
+        <v>11.78005320981035</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>17.63865728521221</v>
+        <v>18.59573177768589</v>
       </c>
       <c r="H26" t="n">
-        <v>16.21085643041471</v>
+        <v>15.13043247144338</v>
       </c>
       <c r="I26" t="n">
-        <v>1.427800854797503</v>
+        <v>3.465299306242507</v>
       </c>
       <c r="J26" t="n">
-        <v>0.004687380152166093</v>
+        <v>-3.383203211589375e-08</v>
       </c>
       <c r="K26" t="n">
-        <v>16.21554381056687</v>
+        <v>15.13043243761135</v>
       </c>
       <c r="L26" t="n">
-        <v>2.943515234808386</v>
+        <v>3.933822174127526</v>
       </c>
       <c r="M26" t="n">
-        <v>0.08960209041833878</v>
+        <v>1.020723841911404e-07</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5333839107897592</v>
+        <v>0.05245140362635002</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8294808934515573</v>
+        <v>1.747162878779365</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.754233083746549</v>
+        <v>10846.42521868227</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -1901,46 +1938,46 @@
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>6.591193711193156</v>
+        <v>-12.09171877772787</v>
       </c>
       <c r="E27" t="n">
-        <v>2.871834386803542</v>
+        <v>18.29232783467762</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>8.672837360440294</v>
+        <v>22.65658416648923</v>
       </c>
       <c r="H27" t="n">
-        <v>9.353825600452012</v>
+        <v>20.06804286532633</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6809882400117182</v>
+        <v>2.588541301162895</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.004085357938812099</v>
+        <v>2.733630164123615e-08</v>
       </c>
       <c r="K27" t="n">
-        <v>9.349740242513199</v>
+        <v>20.06804289266264</v>
       </c>
       <c r="L27" t="n">
-        <v>2.933192008522962</v>
+        <v>3.933822174127518</v>
       </c>
       <c r="M27" t="n">
-        <v>0.079278863966465</v>
+        <v>1.020723765987215e-07</v>
       </c>
       <c r="N27" t="n">
-        <v>2.481817058326824</v>
+        <v>2.03803569286024</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.3952356553719709</v>
+        <v>1.305111847486398</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.404072896377957</v>
+        <v>8102.163086329122</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -1954,46 +1991,46 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>6.060258268142746</v>
+        <v>-21.07737516515695</v>
       </c>
       <c r="E28" t="n">
-        <v>8.470437825337228</v>
+        <v>-21.73273860322199</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>11.17996514380557</v>
+        <v>30.55345411926473</v>
       </c>
       <c r="H28" t="n">
-        <v>11.05273406575787</v>
+        <v>32.71223092398668</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1272310780476946</v>
+        <v>-2.158776804721949</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.004043749792374918</v>
+        <v>4.108717363826022e-08</v>
       </c>
       <c r="K28" t="n">
-        <v>11.0486903159655</v>
+        <v>32.71223096507386</v>
       </c>
       <c r="L28" t="n">
-        <v>2.933671834076236</v>
+        <v>3.933822174127534</v>
       </c>
       <c r="M28" t="n">
-        <v>0.07975868880748749</v>
+        <v>1.020723922424811e-07</v>
       </c>
       <c r="N28" t="n">
-        <v>1.735490813152936</v>
+        <v>7.122701932784885</v>
       </c>
       <c r="O28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.07664356402267787</v>
+        <v>-1.088429713689604</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4648281876275499</v>
+        <v>-6756.995110821968</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2007,46 +2044,46 @@
         <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>15.61652563484574</v>
+        <v>11.41422634931679</v>
       </c>
       <c r="E29" t="n">
-        <v>7.58037840049748</v>
+        <v>27.31241380752315</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>16.38884115579032</v>
+        <v>28.35925320694647</v>
       </c>
       <c r="H29" t="n">
-        <v>16.87057080613789</v>
+        <v>28.76638135120368</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.481729650347571</v>
+        <v>-0.4071281442572072</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.005937198961363151</v>
+        <v>-3.931667250212793e-08</v>
       </c>
       <c r="K29" t="n">
-        <v>16.86463360717653</v>
+        <v>28.76638131188701</v>
       </c>
       <c r="L29" t="n">
-        <v>2.949312255208065</v>
+        <v>3.933822174127529</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09539911150932312</v>
+        <v>1.020723874716947e-07</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8177500081512176</v>
+        <v>5.535939033935382</v>
       </c>
       <c r="O29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.277049371833967</v>
+        <v>-0.205269167841816</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.540442168347105</v>
+        <v>-1274.315445892831</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2060,46 +2097,46 @@
         <v>28</v>
       </c>
       <c r="D30" t="n">
-        <v>-9.693723687364702</v>
+        <v>1.632564786905078</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.147619648382715</v>
+        <v>-1.693978941922325</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>9.715783933962321</v>
+        <v>0.5163230963155445</v>
       </c>
       <c r="H30" t="n">
-        <v>11.09323109136818</v>
+        <v>7.15777297323757</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.377447157405861</v>
+        <v>-6.641449876922025</v>
       </c>
       <c r="J30" t="n">
-        <v>0.001588458313557624</v>
+        <v>-4.331616090367702e-08</v>
       </c>
       <c r="K30" t="n">
-        <v>11.09481954968174</v>
+        <v>7.157772929921409</v>
       </c>
       <c r="L30" t="n">
-        <v>2.931920546365228</v>
+        <v>3.933822174127515</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07800740003585815</v>
+        <v>1.020723728205539e-07</v>
       </c>
       <c r="N30" t="n">
-        <v>1.715519787162776</v>
+        <v>3.153631296900486</v>
       </c>
       <c r="O30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.8053772991653457</v>
+        <v>-3.348540334267912</v>
       </c>
       <c r="Q30" t="n">
-        <v>-4.93750557324795</v>
+        <v>-20787.81251105235</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2113,46 +2150,46 @@
         <v>29</v>
       </c>
       <c r="D31" t="n">
-        <v>14.34476951603071</v>
+        <v>-10.29776502369423</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5447391675731552</v>
+        <v>7.463092368956055</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>14.0727867442805</v>
+        <v>12.51002737892676</v>
       </c>
       <c r="H31" t="n">
-        <v>13.90874796755645</v>
+        <v>11.83157066238005</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1640387767240483</v>
+        <v>0.6784567165467141</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.005625030558064385</v>
+        <v>1.941360117257598e-08</v>
       </c>
       <c r="K31" t="n">
-        <v>13.90312293699839</v>
+        <v>11.83157068179365</v>
       </c>
       <c r="L31" t="n">
-        <v>2.945889006338723</v>
+        <v>3.933822174127515</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0919758677482605</v>
+        <v>1.020723727758241e-07</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4812026633263627</v>
+        <v>1.274135238704901</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.09885098895296876</v>
+        <v>0.3420698299803251</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.559438397440463</v>
+        <v>2123.577076287855</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2166,46 +2203,682 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9307075704026033</v>
+        <v>7.591842758822531</v>
       </c>
       <c r="E32" t="n">
-        <v>9.753552886461975</v>
+        <v>-5.482376897994327</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>10.70225566226142</v>
+        <v>9.592739365266546</v>
       </c>
       <c r="H32" t="n">
-        <v>10.32607905569012</v>
+        <v>9.359221162239805</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3761766065713044</v>
+        <v>0.2335182030267404</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.001902892092771969</v>
+        <v>-4.901883736784813e-08</v>
       </c>
       <c r="K32" t="n">
-        <v>10.32417616359734</v>
+        <v>9.359221113220968</v>
       </c>
       <c r="L32" t="n">
-        <v>2.929499398709667</v>
+        <v>3.933822174127518</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07558625936508179</v>
+        <v>1.020723767593244e-07</v>
       </c>
       <c r="N32" t="n">
-        <v>2.054538325723071</v>
+        <v>2.268352685694876</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2208952727093392</v>
+        <v>0.1177371365218627</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.375186822103147</v>
+        <v>730.914735395509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>31</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.924640630203903</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.119574885302598</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.644784122469007</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.430101379723737</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-2.78531725725473</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-5.006588885545765e-08</v>
+      </c>
+      <c r="K33" t="n">
+        <v>8.430101329657848</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.933822174127517</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.020723755989202e-07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.641983951638913</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-1.404323942162262</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-8718.073997315423</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-6.206197874611312</v>
+      </c>
+      <c r="E34" t="n">
+        <v>22.31628019576578</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="n">
+        <v>21.59693977205388</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20.72891400678293</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.86802576527095</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-4.452628924939731e-09</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20.7289140023303</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.933822174127517</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.020723751368892e-07</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.303794870201226</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4376483108245143</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2716.930369590384</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>33</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-9.57679161945309</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14.04040503195403</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16.99836392869713</v>
+      </c>
+      <c r="H35" t="n">
+        <v>14.90894517635206</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.089418752345068</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.524778069769951e-08</v>
+      </c>
+      <c r="K35" t="n">
+        <v>14.90894519159984</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.933822174127516</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.02072373532006e-07</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.03661629419015731</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.053460176864237</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6539.904072256693</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-11.22740362589908</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-9.231346303046408</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14.9586881689375</v>
+      </c>
+      <c r="H36" t="n">
+        <v>13.31068721568749</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.648000953250007</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.426056643179835e-08</v>
+      </c>
+      <c r="K36" t="n">
+        <v>13.31068723994806</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3.933822174127516</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.020723737752339e-07</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.6793312081818801</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.83090254686694</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5158.261377857004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.996932756823611</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-13.79653451799263</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="n">
+        <v>14.23136905153202</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12.97157922002822</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.259789831503802</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-4.870613493589706e-08</v>
+      </c>
+      <c r="K37" t="n">
+        <v>12.97157917132208</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3.933822174127518</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.020723763716258e-07</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.8156983152158824</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.6351711346579834</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3943.15639411599</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19.21089343106291</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.8386006665221544</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19.24148756668894</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17.34171643341489</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.899771133274051</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-9.538917375348187e-09</v>
+      </c>
+      <c r="K38" t="n">
+        <v>17.34171642387597</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.933822174127531</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.020723897528121e-07</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.9416853320885953</v>
+      </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.9578421063121413</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5946.304503469162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-23.5748263108685</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-11.54109296391725</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="n">
+        <v>25.70302387727502</v>
+      </c>
+      <c r="H39" t="n">
+        <v>27.4828560166298</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-1.779832139354777</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.82767082829047e-08</v>
+      </c>
+      <c r="K39" t="n">
+        <v>27.48285605490651</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.933822174127537</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.020723959919228e-07</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.019789044320838</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.8973703008144402</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-5570.894057347413</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-12.75215359731575</v>
+      </c>
+      <c r="E40" t="n">
+        <v>25.83285277671557</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="n">
+        <v>28.96433826167509</v>
+      </c>
+      <c r="H40" t="n">
+        <v>28.95222697263694</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.01211128903815251</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.920073334802417e-08</v>
+      </c>
+      <c r="K40" t="n">
+        <v>28.95222700183767</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.933822174127521</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.020723798485646e-07</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.610674026812429</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.006106353745109185</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>37.90837790138469</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-16.35321082151363</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.056625987281194</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="n">
+        <v>16.89058784848077</v>
+      </c>
+      <c r="H41" t="n">
+        <v>15.45095281716993</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.439635031310836</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.174754348447573e-08</v>
+      </c>
+      <c r="K41" t="n">
+        <v>15.45095285891748</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3.933822174127521</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.020723798291341e-07</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.1813437734715652</v>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.7258469084240206</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4506.073518545636</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" t="n">
+        <v>26.06564217464059</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.156462640562879</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="n">
+        <v>26.55830513266619</v>
+      </c>
+      <c r="H42" t="n">
+        <v>26.37700998418779</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.181295148478398</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.157329683159261e-08</v>
+      </c>
+      <c r="K42" t="n">
+        <v>26.37700999576109</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.933822174127544</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.020724016095386e-07</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.575090018073423</v>
+      </c>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.09140686048120863</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>567.4557330244087</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="n">
+        <v>41</v>
+      </c>
+      <c r="D43" t="n">
+        <v>17.23406299489677</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-18.71534302127812</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="n">
+        <v>24.10282033731087</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.58957162693866</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-0.4867512896277937</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-1.684542014142987e-08</v>
+      </c>
+      <c r="K43" t="n">
+        <v>24.58957161009324</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.933822174127529</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.020723879474453e-07</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.856299095042059</v>
+      </c>
+      <c r="O43" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-0.2454142258849361</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>-1523.536833350393</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" t="n">
+        <v>42</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-15.23674654061881</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-15.21640986076447</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="n">
+        <v>23.04512706241528</v>
+      </c>
+      <c r="H44" t="n">
+        <v>20.25794479244911</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.78718226996617</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.853256762779022e-08</v>
+      </c>
+      <c r="K44" t="n">
+        <v>20.25794483098168</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.933822174127521</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.020723797826178e-07</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.114401843785655</v>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.405264265294172</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>8723.911365265883</v>
       </c>
     </row>
   </sheetData>

--- a/history_matching/example/iter1/Cuts/RadiusShouldBe15/train_data.xlsx
+++ b/history_matching/example/iter1/Cuts/RadiusShouldBe15/train_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -68,136 +68,142 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20180119_074303.000000</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000001</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000002</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000003</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000004</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000005</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000006</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000007</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000008</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000009</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000010</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000011</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000012</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000013</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000014</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000015</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000016</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000017</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000018</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000019</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000020</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000021</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000022</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000023</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000024</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000025</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000026</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000027</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000028</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000029</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000030</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000031</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000032</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000033</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000034</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000035</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000036</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000037</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000038</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000039</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000040</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000041</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000042</t>
+    <t>Data_20180120_214336.000000</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000001</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000002</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000003</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000004</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000005</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000006</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000007</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000008</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000009</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000010</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000011</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000012</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000013</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000014</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000015</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000016</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000017</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000018</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000019</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000020</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000021</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000022</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000023</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000024</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000025</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000026</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000027</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000028</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000029</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000030</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000031</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000032</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000033</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000034</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000035</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000036</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000037</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000038</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000039</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000040</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000041</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000042</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000043</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000044</t>
   </si>
 </sst>
 </file>
@@ -546,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -613,46 +619,46 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.186099688264044</v>
+        <v>-14.28262220083123</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.139445702561019</v>
+        <v>-10.47825102685486</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.145783012867295</v>
+        <v>17.64576918975835</v>
       </c>
       <c r="H2" t="n">
-        <v>7.253615269822205</v>
+        <v>22.56487044300409</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.107832256954911</v>
+        <v>-4.919101253245739</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.490691390535565e-08</v>
+        <v>-5.394937069062614</v>
       </c>
       <c r="K2" t="n">
-        <v>7.253615224915292</v>
+        <v>17.16993337394148</v>
       </c>
       <c r="L2" t="n">
-        <v>3.933822174127515</v>
+        <v>44.66714888311026</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0207237312335e-07</v>
+        <v>43.69135867056392</v>
       </c>
       <c r="N2" t="n">
-        <v>3.115089788428652</v>
+        <v>0.3167966592496795</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.575308496071165</v>
+        <v>0.07119721599212117</v>
       </c>
       <c r="Q2" t="n">
-        <v>-15987.57212125578</v>
+        <v>0.07198787483385005</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -666,46 +672,46 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>24.07984869323391</v>
+        <v>-3.396496081322873</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.58956938733648</v>
+        <v>-14.43989753599655</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>26.24499798705829</v>
+        <v>15.99662057460847</v>
       </c>
       <c r="H3" t="n">
-        <v>27.11285241181588</v>
+        <v>18.98805053459122</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8678544247575886</v>
+        <v>-2.991429959982748</v>
       </c>
       <c r="J3" t="n">
-        <v>6.862175237448274e-09</v>
+        <v>-4.104020311321648</v>
       </c>
       <c r="K3" t="n">
-        <v>27.11285241867806</v>
+        <v>14.88403022326957</v>
       </c>
       <c r="L3" t="n">
-        <v>3.93382217412754</v>
+        <v>38.2364465250857</v>
       </c>
       <c r="M3" t="n">
-        <v>1.020723978858604e-07</v>
+        <v>37.26065631253937</v>
       </c>
       <c r="N3" t="n">
-        <v>4.870997758790599</v>
+        <v>0.01822594228666631</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4375619241821689</v>
+        <v>0.17992707794826</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2716.393776706067</v>
+        <v>0.1822678367383126</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -719,46 +725,46 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>-9.016405488666004</v>
+        <v>-11.12449365893673</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.823317184306902</v>
+        <v>-18.67802243556289</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3297339723723</v>
+        <v>21.62409178107918</v>
       </c>
       <c r="H4" t="n">
-        <v>10.33520508073548</v>
+        <v>21.52721417134541</v>
       </c>
       <c r="I4" t="n">
-        <v>0.994528891636822</v>
+        <v>0.09687760973376669</v>
       </c>
       <c r="J4" t="n">
-        <v>1.272892722626377e-08</v>
+        <v>-0.006206319095310091</v>
       </c>
       <c r="K4" t="n">
-        <v>10.3352050934644</v>
+        <v>21.5210078522501</v>
       </c>
       <c r="L4" t="n">
-        <v>3.933822174127514</v>
+        <v>36.83727522077984</v>
       </c>
       <c r="M4" t="n">
-        <v>1.020723716993224e-07</v>
+        <v>35.86148500823351</v>
       </c>
       <c r="N4" t="n">
-        <v>1.875875702069566</v>
+        <v>1.043030539998128</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5014296799723392</v>
+        <v>0.01698428281922628</v>
       </c>
       <c r="Q4" t="n">
-        <v>3112.886568908816</v>
+        <v>0.01721380296800885</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -772,46 +778,46 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.859916288097089</v>
+        <v>19.09473044169717</v>
       </c>
       <c r="E5" t="n">
-        <v>-31.32942135452733</v>
+        <v>7.70156207036537</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>33.60200418543344</v>
+        <v>19.587361834645</v>
       </c>
       <c r="H5" t="n">
-        <v>32.94924213567299</v>
+        <v>11.59817961917003</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6527620497604474</v>
+        <v>7.989182215474973</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.395897507043858e-08</v>
+        <v>8.129722596308488</v>
       </c>
       <c r="K5" t="n">
-        <v>32.94924209171401</v>
+        <v>19.72790221547852</v>
       </c>
       <c r="L5" t="n">
-        <v>3.933822174127522</v>
+        <v>34.18657564849298</v>
       </c>
       <c r="M5" t="n">
-        <v>1.020723808826089e-07</v>
+        <v>33.21078543594663</v>
       </c>
       <c r="N5" t="n">
-        <v>7.218012321021144</v>
+        <v>0.783248746181145</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3291149153066654</v>
+        <v>-0.02403661600297568</v>
       </c>
       <c r="Q5" t="n">
-        <v>2043.152598099124</v>
+        <v>-0.02438717825176789</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -825,46 +831,46 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.02079393798419</v>
+        <v>-12.81952127689775</v>
       </c>
       <c r="E6" t="n">
-        <v>-18.75135171052559</v>
+        <v>11.44098012015435</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>23.61158847221721</v>
+        <v>17.41501668391561</v>
       </c>
       <c r="H6" t="n">
-        <v>24.04360947279838</v>
+        <v>22.08414401605554</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4320210005811695</v>
+        <v>-4.669127332139926</v>
       </c>
       <c r="J6" t="n">
-        <v>3.982084798009562e-08</v>
+        <v>-4.920335266310541</v>
       </c>
       <c r="K6" t="n">
-        <v>24.04360951261923</v>
+        <v>17.16380874974499</v>
       </c>
       <c r="L6" t="n">
-        <v>3.933822174127523</v>
+        <v>47.57885360837655</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0207238190164e-07</v>
+        <v>46.60306339583021</v>
       </c>
       <c r="N6" t="n">
-        <v>3.636748813963774</v>
+        <v>0.3065338393376834</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2178198910301953</v>
+        <v>0.03641886151286856</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1352.230644545</v>
+        <v>0.03679816135067882</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -878,46 +884,46 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-22.21519901616071</v>
+        <v>8.522341468257151</v>
       </c>
       <c r="E7" t="n">
-        <v>19.67113524689151</v>
+        <v>-13.72083989057997</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>30.05940074136868</v>
+        <v>15.74166469496863</v>
       </c>
       <c r="H7" t="n">
-        <v>32.06741893873789</v>
+        <v>15.07191590924645</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.008018197369207</v>
+        <v>0.6697487857221844</v>
       </c>
       <c r="J7" t="n">
-        <v>4.064277691757568e-08</v>
+        <v>1.323994336745362</v>
       </c>
       <c r="K7" t="n">
-        <v>32.06741897938066</v>
+        <v>16.39591024599181</v>
       </c>
       <c r="L7" t="n">
-        <v>3.933822174127537</v>
+        <v>33.78518824076898</v>
       </c>
       <c r="M7" t="n">
-        <v>1.020723943734916e-07</v>
+        <v>32.80939802822265</v>
       </c>
       <c r="N7" t="n">
-        <v>6.863400685763197</v>
+        <v>0.2325380881141247</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.01241900946168</v>
+        <v>-0.1125583210795131</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6285.118955854149</v>
+        <v>-0.1142198661608359</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -931,46 +937,46 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>14.71013225950182</v>
+        <v>-28.76919198232598</v>
       </c>
       <c r="E8" t="n">
-        <v>-26.57688483605933</v>
+        <v>8.890382369214663</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>30.62284658747639</v>
+        <v>29.41803461624367</v>
       </c>
       <c r="H8" t="n">
-        <v>31.45755939714243</v>
+        <v>27.32467669825284</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8347128096660441</v>
+        <v>2.093357917990826</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.592072776555766e-08</v>
+        <v>2.64665578951313</v>
       </c>
       <c r="K8" t="n">
-        <v>31.45755937122171</v>
+        <v>29.97133248776597</v>
       </c>
       <c r="L8" t="n">
-        <v>3.933822174127529</v>
+        <v>50.22000827470016</v>
       </c>
       <c r="M8" t="n">
-        <v>1.020723867154073e-07</v>
+        <v>49.24421806215383</v>
       </c>
       <c r="N8" t="n">
-        <v>6.618155001110223</v>
+        <v>2.066830629949205</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4208522979059683</v>
+        <v>-0.07807654907022168</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2612.660202632832</v>
+        <v>-0.0788463106256595</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -984,46 +990,46 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.50780455188965</v>
+        <v>-15.53238305234518</v>
       </c>
       <c r="E9" t="n">
-        <v>-23.35173533077449</v>
+        <v>-6.593957180015353</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>26.93047520653213</v>
+        <v>15.5140147996286</v>
       </c>
       <c r="H9" t="n">
-        <v>26.73266078823161</v>
+        <v>22.9755003994621</v>
       </c>
       <c r="I9" t="n">
-        <v>0.197814418300517</v>
+        <v>-7.4614855998335</v>
       </c>
       <c r="J9" t="n">
-        <v>3.257013686277855e-08</v>
+        <v>-6.32194508195033</v>
       </c>
       <c r="K9" t="n">
-        <v>26.73266082080175</v>
+        <v>16.65355531751177</v>
       </c>
       <c r="L9" t="n">
-        <v>3.933822174127521</v>
+        <v>47.54128707759335</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02072379858368e-07</v>
+        <v>46.56549686504701</v>
       </c>
       <c r="N9" t="n">
-        <v>4.718109540792438</v>
+        <v>0.2343376400208544</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09973567005880241</v>
+        <v>-0.1652701054308052</v>
       </c>
       <c r="Q9" t="n">
-        <v>619.1612259089213</v>
+        <v>-0.1669927632284297</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1037,46 +1043,46 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>23.73451069352058</v>
+        <v>4.490319273659907</v>
       </c>
       <c r="E10" t="n">
-        <v>5.534927670994279</v>
+        <v>13.2521497426684</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>23.23343656808299</v>
+        <v>13.13274115676837</v>
       </c>
       <c r="H10" t="n">
-        <v>23.48520708255433</v>
+        <v>16.39670464478696</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2517705144713354</v>
+        <v>-3.263963488018588</v>
       </c>
       <c r="J10" t="n">
-        <v>6.169137500765327e-09</v>
+        <v>-3.242936139417506</v>
       </c>
       <c r="K10" t="n">
-        <v>23.48520708872346</v>
+        <v>13.15376850536945</v>
       </c>
       <c r="L10" t="n">
-        <v>3.933822174127539</v>
+        <v>40.25032250820395</v>
       </c>
       <c r="M10" t="n">
-        <v>1.020723976927631e-07</v>
+        <v>39.27453229565761</v>
       </c>
       <c r="N10" t="n">
-        <v>3.412195846480628</v>
+        <v>0.2831979090263172</v>
       </c>
       <c r="O10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1269397141386713</v>
+        <v>-0.003314361171284084</v>
       </c>
       <c r="Q10" t="n">
-        <v>-788.0444590186383</v>
+        <v>-0.003355281820262595</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1090,46 +1096,46 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-24.53380220870584</v>
+        <v>-22.23614077501719</v>
       </c>
       <c r="E11" t="n">
-        <v>12.12810024526132</v>
+        <v>13.4551717929832</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>29.40932511489485</v>
+        <v>25.14144328642549</v>
       </c>
       <c r="H11" t="n">
-        <v>29.2787070458993</v>
+        <v>25.1781327978375</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1306180689955525</v>
+        <v>-0.03668951141201049</v>
       </c>
       <c r="J11" t="n">
-        <v>3.649417922412153e-08</v>
+        <v>0.2813896310449405</v>
       </c>
       <c r="K11" t="n">
-        <v>29.27870708239347</v>
+        <v>25.45952242888244</v>
       </c>
       <c r="L11" t="n">
-        <v>3.93382217412754</v>
+        <v>48.01408477240629</v>
       </c>
       <c r="M11" t="n">
-        <v>1.020723984266272e-07</v>
+        <v>47.03829455985996</v>
       </c>
       <c r="N11" t="n">
-        <v>5.74196298218885</v>
+        <v>1.475308912221688</v>
       </c>
       <c r="O11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.06585606474062591</v>
+        <v>-0.04590403525042323</v>
       </c>
       <c r="Q11" t="n">
-        <v>408.8358562740019</v>
+        <v>-0.04637772148658104</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1143,46 +1149,46 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>2.314465242766595</v>
+        <v>-19.70552744579863</v>
       </c>
       <c r="E12" t="n">
-        <v>8.694287936571882</v>
+        <v>-0.5796256416992236</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>9.325313624883758</v>
+        <v>21.24948150636661</v>
       </c>
       <c r="H12" t="n">
-        <v>8.889661883643612</v>
+        <v>24.34665720798344</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4356517412401466</v>
+        <v>-3.097175701616827</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.554943435388997e-08</v>
+        <v>-4.656151951746858</v>
       </c>
       <c r="K12" t="n">
-        <v>8.889661838094177</v>
+        <v>19.69050525623658</v>
       </c>
       <c r="L12" t="n">
-        <v>3.933822174127517</v>
+        <v>50.6252960159524</v>
       </c>
       <c r="M12" t="n">
-        <v>1.020723743143283e-07</v>
+        <v>49.64950580340606</v>
       </c>
       <c r="N12" t="n">
-        <v>2.457178743976164</v>
+        <v>0.6450497646386505</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2196504703505028</v>
+        <v>0.2191067269071117</v>
       </c>
       <c r="Q12" t="n">
-        <v>1363.59497165744</v>
+        <v>0.2212493655876435</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1196,46 +1202,46 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>7.965501321120925</v>
+        <v>-33.39683531992438</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.585598447696029</v>
+        <v>-8.520053328038045</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>6.962327857642332</v>
+        <v>34.20800292712482</v>
       </c>
       <c r="H13" t="n">
-        <v>9.047566422641523</v>
+        <v>28.84516678235116</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.085238564999191</v>
+        <v>5.362836144773652</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.874543276671825e-08</v>
+        <v>6.188553814643018</v>
       </c>
       <c r="K13" t="n">
-        <v>9.047566373896091</v>
+        <v>35.03372059699418</v>
       </c>
       <c r="L13" t="n">
-        <v>3.933822174127519</v>
+        <v>46.73592556112079</v>
       </c>
       <c r="M13" t="n">
-        <v>1.020723770448414e-07</v>
+        <v>45.76013534857444</v>
       </c>
       <c r="N13" t="n">
-        <v>2.393679857553016</v>
+        <v>2.862371199180791</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.051352559032076</v>
+        <v>-0.1207830951159106</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6526.819821839931</v>
+        <v>-0.1220640929252618</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1249,46 +1255,46 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.303288666319887</v>
+        <v>15.65911912085967</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.87979074122815</v>
+        <v>-10.2159088586972</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>20.61503469974378</v>
+        <v>20.45437214060491</v>
       </c>
       <c r="H14" t="n">
-        <v>18.97251635070643</v>
+        <v>12.72700752682385</v>
       </c>
       <c r="I14" t="n">
-        <v>1.642518349037353</v>
+        <v>7.727364613781063</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.393659002237656e-08</v>
+        <v>6.435938870976938</v>
       </c>
       <c r="K14" t="n">
-        <v>18.97251633676984</v>
+        <v>19.16294639780078</v>
       </c>
       <c r="L14" t="n">
-        <v>3.933822174127516</v>
+        <v>32.32945895138586</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02072374127033e-07</v>
+        <v>31.35366873883952</v>
       </c>
       <c r="N14" t="n">
-        <v>1.597486496518939</v>
+        <v>0.7079322905689361</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8281383020261091</v>
+        <v>0.2271277616525512</v>
       </c>
       <c r="Q14" t="n">
-        <v>5141.100875922568</v>
+        <v>0.2306350223799978</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1302,46 +1308,46 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.9394739177012</v>
+        <v>-24.17501366926623</v>
       </c>
       <c r="E15" t="n">
-        <v>33.20049266139981</v>
+        <v>-1.310707860344252</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>35.30718275687315</v>
+        <v>23.8613951310281</v>
       </c>
       <c r="H15" t="n">
-        <v>37.26659892430052</v>
+        <v>25.81518211105502</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.959416167427371</v>
+        <v>-1.953786980026916</v>
       </c>
       <c r="J15" t="n">
-        <v>1.053708997859153e-08</v>
+        <v>-1.559477423640385</v>
       </c>
       <c r="K15" t="n">
-        <v>37.26659893483762</v>
+        <v>24.25570468741463</v>
       </c>
       <c r="L15" t="n">
-        <v>3.933822174127522</v>
+        <v>50.77457733032342</v>
       </c>
       <c r="M15" t="n">
-        <v>1.020723804752123e-07</v>
+        <v>49.79878711777708</v>
       </c>
       <c r="N15" t="n">
-        <v>8.954171136456416</v>
+        <v>1.271074136472552</v>
       </c>
       <c r="O15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9879144265053926</v>
+        <v>-0.05533681311828886</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6132.994396080207</v>
+        <v>-0.05587633596797741</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1355,46 +1361,46 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08419433195268056</v>
+        <v>-14.99053143848747</v>
       </c>
       <c r="E16" t="n">
-        <v>-30.95110736126681</v>
+        <v>10.31374630003906</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>29.73430230241554</v>
+        <v>17.10082626181099</v>
       </c>
       <c r="H16" t="n">
-        <v>31.69976726845681</v>
+        <v>22.7974659344398</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.965464966041271</v>
+        <v>-5.696639672628809</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.251562860266271e-08</v>
+        <v>-4.667102645524949</v>
       </c>
       <c r="K16" t="n">
-        <v>31.69976723594118</v>
+        <v>18.13036328891485</v>
       </c>
       <c r="L16" t="n">
-        <v>3.933822174127521</v>
+        <v>48.56949341160629</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02072378816159e-07</v>
+        <v>47.59370319905995</v>
       </c>
       <c r="N16" t="n">
-        <v>6.715555177834148</v>
+        <v>0.4391163177861435</v>
       </c>
       <c r="O16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.990964137408311</v>
+        <v>-0.1477271038517094</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6151.927118153078</v>
+        <v>-0.149233808190028</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1408,46 +1414,46 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>19.79603406496537</v>
+        <v>-16.76080713315563</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.700193283887272</v>
+        <v>2.934367234858001</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>21.33400885121691</v>
+        <v>17.76612218867494</v>
       </c>
       <c r="H17" t="n">
-        <v>19.27796628346238</v>
+        <v>23.37911980088926</v>
       </c>
       <c r="I17" t="n">
-        <v>2.056042567754535</v>
+        <v>-5.612997612214322</v>
       </c>
       <c r="J17" t="n">
-        <v>-7.12845748830274e-09</v>
+        <v>-6.137387638717903</v>
       </c>
       <c r="K17" t="n">
-        <v>19.27796627633392</v>
+        <v>17.24173216217136</v>
       </c>
       <c r="L17" t="n">
-        <v>3.933822174127532</v>
+        <v>50.59138036954788</v>
       </c>
       <c r="M17" t="n">
-        <v>1.020723905163169e-07</v>
+        <v>49.61559015700155</v>
       </c>
       <c r="N17" t="n">
-        <v>1.720318503350383</v>
+        <v>0.3083874143198839</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.03663231123584</v>
+        <v>0.07372523381612436</v>
       </c>
       <c r="Q17" t="n">
-        <v>6435.435774923643</v>
+        <v>0.07444668129356234</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1461,46 +1467,46 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.111771209066959</v>
+        <v>-33.19092949680497</v>
       </c>
       <c r="E18" t="n">
-        <v>26.44239633506925</v>
+        <v>-13.99193597541259</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>26.32306066491322</v>
+        <v>35.74757982217823</v>
       </c>
       <c r="H18" t="n">
-        <v>25.35550078319443</v>
+        <v>28.77751295955814</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9675598817187918</v>
+        <v>6.970066862620087</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.078177464696814e-08</v>
+        <v>7.15387769226309</v>
       </c>
       <c r="K18" t="n">
-        <v>25.35550077241265</v>
+        <v>35.93139065182123</v>
       </c>
       <c r="L18" t="n">
-        <v>3.933822174127518</v>
+        <v>42.86168342977682</v>
       </c>
       <c r="M18" t="n">
-        <v>1.020723768637487e-07</v>
+        <v>41.88589321723047</v>
       </c>
       <c r="N18" t="n">
-        <v>4.164305756404272</v>
+        <v>3.116402659044617</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4878322364890945</v>
+        <v>-0.02807608076846717</v>
       </c>
       <c r="Q18" t="n">
-        <v>3028.473261724226</v>
+        <v>-0.02840123364881722</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1514,46 +1520,46 @@
         <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.980370715859571</v>
+        <v>-11.37494736052879</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1087881473155221</v>
+        <v>-9.703988592059773</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>8.177566208936263</v>
+        <v>14.4540553329321</v>
       </c>
       <c r="H19" t="n">
-        <v>9.15622519750201</v>
+        <v>21.60950494918096</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9786589885657477</v>
+        <v>-7.155449616248859</v>
       </c>
       <c r="J19" t="n">
-        <v>6.651184586095754e-09</v>
+        <v>-6.804066440619479</v>
       </c>
       <c r="K19" t="n">
-        <v>9.156225204153195</v>
+        <v>14.80543850856148</v>
       </c>
       <c r="L19" t="n">
-        <v>3.933822174127513</v>
+        <v>44.57358637594913</v>
       </c>
       <c r="M19" t="n">
-        <v>1.020723710599904e-07</v>
+        <v>43.59779616340279</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34998437606271</v>
+        <v>0.02843312205849841</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4934282726033588</v>
+        <v>-0.0526310669362596</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3063.213664181071</v>
+        <v>-0.05321679251428019</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1567,46 +1573,46 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>20.24622118548824</v>
+        <v>-1.225494747373958</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.801395121028833</v>
+        <v>14.40743708062358</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>21.15690245477524</v>
+        <v>15.10783915272085</v>
       </c>
       <c r="H20" t="n">
-        <v>21.17896697865268</v>
+        <v>18.27473151667687</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02206452387744307</v>
+        <v>-3.166892363956023</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.351297029019794e-09</v>
+        <v>-4.163057690195883</v>
       </c>
       <c r="K20" t="n">
-        <v>21.17896697330139</v>
+        <v>14.11167382648099</v>
       </c>
       <c r="L20" t="n">
-        <v>3.933822174127533</v>
+        <v>42.14183277880024</v>
       </c>
       <c r="M20" t="n">
-        <v>1.020723913238547e-07</v>
+        <v>41.16604256625391</v>
       </c>
       <c r="N20" t="n">
-        <v>2.484776767541673</v>
+        <v>0.1333278636566871</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.01112466887382778</v>
+        <v>0.1534527625732455</v>
       </c>
       <c r="Q20" t="n">
-        <v>-69.06218434023478</v>
+        <v>0.1552608150484107</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1620,46 +1626,46 @@
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>6.748994980594944</v>
+        <v>-19.20401189932265</v>
       </c>
       <c r="E21" t="n">
-        <v>-25.20939250478221</v>
+        <v>1.84865425145999</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>27.54423155893729</v>
+        <v>18.66636950730562</v>
       </c>
       <c r="H21" t="n">
-        <v>24.71126723348624</v>
+        <v>24.18187583660109</v>
       </c>
       <c r="I21" t="n">
-        <v>2.832964325451051</v>
+        <v>-5.515506329295466</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.599692633856438e-08</v>
+        <v>-4.8421771453467</v>
       </c>
       <c r="K21" t="n">
-        <v>24.71126718748931</v>
+        <v>19.33969869125439</v>
       </c>
       <c r="L21" t="n">
-        <v>3.933822174127521</v>
+        <v>50.917676415626</v>
       </c>
       <c r="M21" t="n">
-        <v>1.020723796599213e-07</v>
+        <v>49.94188620307966</v>
       </c>
       <c r="N21" t="n">
-        <v>3.90523710437807</v>
+        <v>0.5951627430908273</v>
       </c>
       <c r="O21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.428347077973344</v>
+        <v>-0.09436113368758954</v>
       </c>
       <c r="Q21" t="n">
-        <v>8867.209977730949</v>
+        <v>-0.0952785124475779</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1673,46 +1679,46 @@
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>-18.64576216183469</v>
+        <v>-13.14406127969196</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.306020405177777</v>
+        <v>-11.0246080494157</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>20.15856758020352</v>
+        <v>16.02125957185698</v>
       </c>
       <c r="H22" t="n">
-        <v>18.86887516560614</v>
+        <v>22.19077709474002</v>
       </c>
       <c r="I22" t="n">
-        <v>1.289692414597379</v>
+        <v>-6.169517522883037</v>
       </c>
       <c r="J22" t="n">
-        <v>4.397906650746034e-08</v>
+        <v>-5.541161318429414</v>
       </c>
       <c r="K22" t="n">
-        <v>18.86887520958521</v>
+        <v>16.6496157763106</v>
       </c>
       <c r="L22" t="n">
-        <v>3.933822174127526</v>
+        <v>43.99507046325802</v>
       </c>
       <c r="M22" t="n">
-        <v>1.020723844603938e-07</v>
+        <v>43.01928025071169</v>
       </c>
       <c r="N22" t="n">
-        <v>1.555808807335141</v>
+        <v>0.2425772557577667</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6502476161094943</v>
+        <v>-0.09473356892212914</v>
       </c>
       <c r="Q22" t="n">
-        <v>4036.751363091683</v>
+        <v>-0.09580194750664946</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1726,46 +1732,46 @@
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>27.08979516205517</v>
+        <v>2.937132126698614</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.277371908924778</v>
+        <v>9.723737769914349</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>27.21659702087382</v>
+        <v>10.63776135657066</v>
       </c>
       <c r="H23" t="n">
-        <v>28.40319585559905</v>
+        <v>16.90703041611773</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.186598834725231</v>
+        <v>-6.269269059547067</v>
       </c>
       <c r="J23" t="n">
-        <v>1.313679244110323e-08</v>
+        <v>-6.101878274779636</v>
       </c>
       <c r="K23" t="n">
-        <v>28.40319586873584</v>
+        <v>10.80515214133809</v>
       </c>
       <c r="L23" t="n">
-        <v>3.933822174127545</v>
+        <v>42.57767258593324</v>
       </c>
       <c r="M23" t="n">
-        <v>1.020724031747435e-07</v>
+        <v>41.60188237338689</v>
       </c>
       <c r="N23" t="n">
-        <v>5.389889580143073</v>
+        <v>0.6265317997009449</v>
       </c>
       <c r="O23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5982690831385115</v>
+        <v>-0.02565314325780564</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3714.067157848331</v>
+        <v>-0.02595225229686961</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1779,46 +1785,46 @@
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.28982422068739</v>
+        <v>-36.38126126151729</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.942749773635683</v>
+        <v>-4.372050048544168</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>12.6025429531584</v>
+        <v>38.02384896703593</v>
       </c>
       <c r="H24" t="n">
-        <v>12.10057890476043</v>
+        <v>29.82575014193063</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5019640483979746</v>
+        <v>8.198098825105298</v>
       </c>
       <c r="J24" t="n">
-        <v>2.916708169968913e-08</v>
+        <v>7.944653028174734</v>
       </c>
       <c r="K24" t="n">
-        <v>12.10057893392751</v>
+        <v>37.77040317010537</v>
       </c>
       <c r="L24" t="n">
-        <v>3.933822174127516</v>
+        <v>48.47831638125182</v>
       </c>
       <c r="M24" t="n">
-        <v>1.020723741514435e-07</v>
+        <v>47.50252616870547</v>
       </c>
       <c r="N24" t="n">
-        <v>1.165957697367102</v>
+        <v>3.197021050525727</v>
       </c>
       <c r="O24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2530843124404498</v>
+        <v>0.03640083357636694</v>
       </c>
       <c r="Q24" t="n">
-        <v>1571.153003104612</v>
+        <v>0.03677280345087379</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1832,46 +1838,46 @@
         <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>15.44367982075539</v>
+        <v>-43.63304568169299</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.56306782461934</v>
+        <v>-1.582325195667281</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>18.98484567362867</v>
+        <v>45.37468232811548</v>
       </c>
       <c r="H25" t="n">
-        <v>17.87910137035499</v>
+        <v>32.20844593296325</v>
       </c>
       <c r="I25" t="n">
-        <v>1.105744303273681</v>
+        <v>13.16623639515223</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.475694622525997e-08</v>
+        <v>12.62698032300837</v>
       </c>
       <c r="K25" t="n">
-        <v>17.87910134559804</v>
+        <v>44.83542625597163</v>
       </c>
       <c r="L25" t="n">
-        <v>3.933822174127527</v>
+        <v>47.81306174953137</v>
       </c>
       <c r="M25" t="n">
-        <v>1.020723848191226e-07</v>
+        <v>46.83727153698504</v>
       </c>
       <c r="N25" t="n">
-        <v>1.157786433533515</v>
+        <v>4.216708153022419</v>
       </c>
       <c r="O25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.557503192008339</v>
+        <v>0.07798691960790882</v>
       </c>
       <c r="Q25" t="n">
-        <v>3460.99195223197</v>
+        <v>0.0787951071075377</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1885,46 +1891,46 @@
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>13.39850066047773</v>
+        <v>-17.74467794665309</v>
       </c>
       <c r="E26" t="n">
-        <v>11.78005320981035</v>
+        <v>4.63889640491044</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>18.59573177768589</v>
+        <v>18.03354474207675</v>
       </c>
       <c r="H26" t="n">
-        <v>15.13043247144338</v>
+        <v>23.70238711144501</v>
       </c>
       <c r="I26" t="n">
-        <v>3.465299306242507</v>
+        <v>-5.668842369368257</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.383203211589375e-08</v>
+        <v>-5.263715423472406</v>
       </c>
       <c r="K26" t="n">
-        <v>15.13043243761135</v>
+        <v>18.4386716879726</v>
       </c>
       <c r="L26" t="n">
-        <v>3.933822174127526</v>
+        <v>50.65253766892389</v>
       </c>
       <c r="M26" t="n">
-        <v>1.020723841911404e-07</v>
+        <v>49.67674745637755</v>
       </c>
       <c r="N26" t="n">
-        <v>0.05245140362635002</v>
+        <v>0.4727727760627649</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.747162878779365</v>
+        <v>-0.0569233598409459</v>
       </c>
       <c r="Q26" t="n">
-        <v>10846.42521868227</v>
+        <v>-0.05747970803894756</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -1938,46 +1944,46 @@
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>-12.09171877772787</v>
+        <v>-3.10208073595745</v>
       </c>
       <c r="E27" t="n">
-        <v>18.29232783467762</v>
+        <v>-18.32642694348243</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>22.65658416648923</v>
+        <v>18.31454122305377</v>
       </c>
       <c r="H27" t="n">
-        <v>20.06804286532633</v>
+        <v>18.89131541898768</v>
       </c>
       <c r="I27" t="n">
-        <v>2.588541301162895</v>
+        <v>-0.5767741959339112</v>
       </c>
       <c r="J27" t="n">
-        <v>2.733630164123615e-08</v>
+        <v>0.01245543156901407</v>
       </c>
       <c r="K27" t="n">
-        <v>20.06804289266264</v>
+        <v>18.90377085055669</v>
       </c>
       <c r="L27" t="n">
-        <v>3.933822174127518</v>
+        <v>34.76644753021627</v>
       </c>
       <c r="M27" t="n">
-        <v>1.020723765987215e-07</v>
+        <v>33.79065731766993</v>
       </c>
       <c r="N27" t="n">
-        <v>2.03803569286024</v>
+        <v>0.6416333783978507</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.305111847486398</v>
+        <v>-0.09993196280544867</v>
       </c>
       <c r="Q27" t="n">
-        <v>8102.163086329122</v>
+        <v>-0.1013645871323274</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -1991,46 +1997,46 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>-21.07737516515695</v>
+        <v>-10.70442193834487</v>
       </c>
       <c r="E28" t="n">
-        <v>-21.73273860322199</v>
+        <v>7.343261760773358</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>30.55345411926473</v>
+        <v>14.60656956351769</v>
       </c>
       <c r="H28" t="n">
-        <v>32.71223092398668</v>
+        <v>21.38919253934525</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.158776804721949</v>
+        <v>-6.782622975827556</v>
       </c>
       <c r="J28" t="n">
-        <v>4.108717363826022e-08</v>
+        <v>-7.558857304749035</v>
       </c>
       <c r="K28" t="n">
-        <v>32.71223096507386</v>
+        <v>13.83033523459621</v>
       </c>
       <c r="L28" t="n">
-        <v>3.933822174127534</v>
+        <v>48.63138972066233</v>
       </c>
       <c r="M28" t="n">
-        <v>1.020723922424811e-07</v>
+        <v>47.65559950811599</v>
       </c>
       <c r="N28" t="n">
-        <v>7.122701932784885</v>
+        <v>0.1639766181271109</v>
       </c>
       <c r="O28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.088429713689604</v>
+        <v>0.1113100826624783</v>
       </c>
       <c r="Q28" t="n">
-        <v>-6756.995110821968</v>
+        <v>0.1124438939297553</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2044,46 +2050,46 @@
         <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>11.41422634931679</v>
+        <v>16.78947459882893</v>
       </c>
       <c r="E29" t="n">
-        <v>27.31241380752315</v>
+        <v>7.557053520761841</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>28.35925320694647</v>
+        <v>17.37374458801332</v>
       </c>
       <c r="H29" t="n">
-        <v>28.76638135120368</v>
+        <v>12.35561021497949</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4071281442572072</v>
+        <v>5.018134373033828</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.931667250212793e-08</v>
+        <v>4.815156543230962</v>
       </c>
       <c r="K29" t="n">
-        <v>28.76638131188701</v>
+        <v>17.17076675821045</v>
       </c>
       <c r="L29" t="n">
-        <v>3.933822174127529</v>
+        <v>35.45184929118661</v>
       </c>
       <c r="M29" t="n">
-        <v>1.020723874716947e-07</v>
+        <v>34.47605907864027</v>
       </c>
       <c r="N29" t="n">
-        <v>5.535939033935382</v>
+        <v>0.3535345282255869</v>
       </c>
       <c r="O29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.205269167841816</v>
+        <v>0.03409016926524057</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1274.315445892831</v>
+        <v>0.03456923720927566</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2097,46 +2103,46 @@
         <v>28</v>
       </c>
       <c r="D30" t="n">
-        <v>1.632564786905078</v>
+        <v>-27.25288880650182</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.693978941922325</v>
+        <v>6.190441661789564</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5163230963155445</v>
+        <v>27.91091457606236</v>
       </c>
       <c r="H30" t="n">
-        <v>7.15777297323757</v>
+        <v>26.82646977625528</v>
       </c>
       <c r="I30" t="n">
-        <v>-6.641449876922025</v>
+        <v>1.084444799807077</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.331616090367702e-08</v>
+        <v>1.183282718260328</v>
       </c>
       <c r="K30" t="n">
-        <v>7.157772929921409</v>
+        <v>28.00975249451561</v>
       </c>
       <c r="L30" t="n">
-        <v>3.933822174127515</v>
+        <v>50.99286609184425</v>
       </c>
       <c r="M30" t="n">
-        <v>1.020723728205539e-07</v>
+        <v>50.01707587929791</v>
       </c>
       <c r="N30" t="n">
-        <v>3.153631296900486</v>
+        <v>1.782946540147516</v>
       </c>
       <c r="O30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-3.348540334267912</v>
+        <v>-0.01384104495604737</v>
       </c>
       <c r="Q30" t="n">
-        <v>-20787.81251105235</v>
+        <v>-0.01397540625554461</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2150,46 +2156,46 @@
         <v>29</v>
       </c>
       <c r="D31" t="n">
-        <v>-10.29776502369423</v>
+        <v>-0.2145923258120064</v>
       </c>
       <c r="E31" t="n">
-        <v>7.463092368956055</v>
+        <v>18.36427384058495</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>12.51002737892676</v>
+        <v>17.544405971428</v>
       </c>
       <c r="H31" t="n">
-        <v>11.83157066238005</v>
+        <v>17.94258251645301</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6784567165467141</v>
+        <v>-0.398176545025013</v>
       </c>
       <c r="J31" t="n">
-        <v>1.941360117257598e-08</v>
+        <v>-0.6354156749005376</v>
       </c>
       <c r="K31" t="n">
-        <v>11.83157068179365</v>
+        <v>17.30716684155247</v>
       </c>
       <c r="L31" t="n">
-        <v>3.933822174127515</v>
+        <v>39.51455063952193</v>
       </c>
       <c r="M31" t="n">
-        <v>1.020723727758241e-07</v>
+        <v>38.53876042697559</v>
       </c>
       <c r="N31" t="n">
-        <v>1.274135238704901</v>
+        <v>0.3570056545806225</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3420698299803251</v>
+        <v>0.03774051296474316</v>
       </c>
       <c r="Q31" t="n">
-        <v>2123.577076287855</v>
+        <v>0.03821531569465752</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2203,46 +2209,46 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>7.591842758822531</v>
+        <v>6.429852593260819</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.482376897994327</v>
+        <v>12.97376845955762</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>9.592739365266546</v>
+        <v>12.11047704320138</v>
       </c>
       <c r="H32" t="n">
-        <v>9.359221162239805</v>
+        <v>15.75943833770765</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2335182030267404</v>
+        <v>-3.648961294506273</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.901883736784813e-08</v>
+        <v>-2.410963332780826</v>
       </c>
       <c r="K32" t="n">
-        <v>9.359221113220968</v>
+        <v>13.34847500492683</v>
       </c>
       <c r="L32" t="n">
-        <v>3.933822174127518</v>
+        <v>39.45660607121567</v>
       </c>
       <c r="M32" t="n">
-        <v>1.020723767593244e-07</v>
+        <v>38.48081585866932</v>
       </c>
       <c r="N32" t="n">
-        <v>2.268352685694876</v>
+        <v>0.255730616684792</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1177371365218627</v>
+        <v>-0.1970879474836212</v>
       </c>
       <c r="Q32" t="n">
-        <v>730.914735395509</v>
+        <v>-0.199571165687266</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2256,46 +2262,46 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>4.924640630203903</v>
+        <v>18.0202976251165</v>
       </c>
       <c r="E33" t="n">
-        <v>6.119574885302598</v>
+        <v>-9.5158163906206</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>5.644784122469007</v>
+        <v>19.64407672468142</v>
       </c>
       <c r="H33" t="n">
-        <v>8.430101379723737</v>
+        <v>11.95120259965075</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.78531725725473</v>
+        <v>7.692874125030674</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.006588885545765e-08</v>
+        <v>9.407324762907912</v>
       </c>
       <c r="K33" t="n">
-        <v>8.430101329657848</v>
+        <v>21.35852736255866</v>
       </c>
       <c r="L33" t="n">
-        <v>3.933822174127517</v>
+        <v>31.44765956811764</v>
       </c>
       <c r="M33" t="n">
-        <v>1.020723755989202e-07</v>
+        <v>30.4718693555713</v>
       </c>
       <c r="N33" t="n">
-        <v>2.641983951638913</v>
+        <v>1.095359490054262</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-1.404323942162262</v>
+        <v>-0.3057249064560016</v>
       </c>
       <c r="Q33" t="n">
-        <v>-8718.073997315423</v>
+        <v>-0.310581395274803</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2309,46 +2315,46 @@
         <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>-6.206197874611312</v>
+        <v>-16.64047837101648</v>
       </c>
       <c r="E34" t="n">
-        <v>22.31628019576578</v>
+        <v>2.2632736197816</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>21.59693977205388</v>
+        <v>17.11061053644111</v>
       </c>
       <c r="H34" t="n">
-        <v>20.72891400678293</v>
+        <v>23.3395837614158</v>
       </c>
       <c r="I34" t="n">
-        <v>0.86802576527095</v>
+        <v>-6.228973224974691</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.452628924939731e-09</v>
+        <v>-6.30138186969684</v>
       </c>
       <c r="K34" t="n">
-        <v>20.7289140023303</v>
+        <v>17.03820189171896</v>
       </c>
       <c r="L34" t="n">
-        <v>3.933822174127517</v>
+        <v>50.55754770112217</v>
       </c>
       <c r="M34" t="n">
-        <v>1.020723751368892e-07</v>
+        <v>49.58175748857583</v>
       </c>
       <c r="N34" t="n">
-        <v>2.303794870201226</v>
+        <v>0.2804782572886387</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.4376483108245143</v>
+        <v>0.01018350822947282</v>
       </c>
       <c r="Q34" t="n">
-        <v>2716.930369590384</v>
+        <v>0.01028322788924588</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2362,46 +2368,46 @@
         <v>33</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.57679161945309</v>
+        <v>14.80870798052839</v>
       </c>
       <c r="E35" t="n">
-        <v>14.04040503195403</v>
+        <v>2.364105446404125</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
       </c>
       <c r="G35" t="n">
-        <v>16.99836392869713</v>
+        <v>14.05255176123007</v>
       </c>
       <c r="H35" t="n">
-        <v>14.90894517635206</v>
+        <v>13.0064244161452</v>
       </c>
       <c r="I35" t="n">
-        <v>2.089418752345068</v>
+        <v>1.046127345084869</v>
       </c>
       <c r="J35" t="n">
-        <v>1.524778069769951e-08</v>
+        <v>1.294788336084069</v>
       </c>
       <c r="K35" t="n">
-        <v>14.90894519159984</v>
+        <v>14.30121275222927</v>
       </c>
       <c r="L35" t="n">
-        <v>3.933822174127516</v>
+        <v>37.01520034955876</v>
       </c>
       <c r="M35" t="n">
-        <v>1.02072373532006e-07</v>
+        <v>36.03941013701242</v>
       </c>
       <c r="N35" t="n">
-        <v>0.03661629419015731</v>
+        <v>0.1115169959895996</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.053460176864237</v>
+        <v>-0.04087122060198098</v>
       </c>
       <c r="Q35" t="n">
-        <v>6539.904072256693</v>
+        <v>-0.04142083246973761</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2415,46 +2421,46 @@
         <v>34</v>
       </c>
       <c r="D36" t="n">
-        <v>-11.22740362589908</v>
+        <v>4.244992349882806</v>
       </c>
       <c r="E36" t="n">
-        <v>-9.231346303046408</v>
+        <v>-17.03689010950576</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
       </c>
       <c r="G36" t="n">
-        <v>14.9586881689375</v>
+        <v>19.19669121780489</v>
       </c>
       <c r="H36" t="n">
-        <v>13.31068721568749</v>
+        <v>16.47731093350734</v>
       </c>
       <c r="I36" t="n">
-        <v>1.648000953250007</v>
+        <v>2.719380284297547</v>
       </c>
       <c r="J36" t="n">
-        <v>2.426056643179835e-08</v>
+        <v>1.638806677314351</v>
       </c>
       <c r="K36" t="n">
-        <v>13.31068723994806</v>
+        <v>18.11611761082169</v>
       </c>
       <c r="L36" t="n">
-        <v>3.933822174127516</v>
+        <v>33.18905381590765</v>
       </c>
       <c r="M36" t="n">
-        <v>1.020723737752339e-07</v>
+        <v>32.21326360336131</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6793312081818801</v>
+        <v>0.5234470802497151</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.83090254686694</v>
+        <v>0.1875672106712254</v>
       </c>
       <c r="Q36" t="n">
-        <v>5158.261377857004</v>
+        <v>0.190386869307802</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2468,46 +2474,46 @@
         <v>35</v>
       </c>
       <c r="D37" t="n">
-        <v>5.996932756823611</v>
+        <v>20.3862937107593</v>
       </c>
       <c r="E37" t="n">
-        <v>-13.79653451799263</v>
+        <v>-2.016250913793499</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>14.23136905153202</v>
+        <v>23.31532944974296</v>
       </c>
       <c r="H37" t="n">
-        <v>12.97157922002822</v>
+        <v>11.17381477505182</v>
       </c>
       <c r="I37" t="n">
-        <v>1.259789831503802</v>
+        <v>12.14151467469114</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.870613493589706e-08</v>
+        <v>9.972794767017628</v>
       </c>
       <c r="K37" t="n">
-        <v>12.97157917132208</v>
+        <v>21.14660954206945</v>
       </c>
       <c r="L37" t="n">
-        <v>3.933822174127518</v>
+        <v>32.86363690733452</v>
       </c>
       <c r="M37" t="n">
-        <v>1.020723763716258e-07</v>
+        <v>31.88784669478819</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8156983152158824</v>
+        <v>1.037284095121336</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.6351711346579834</v>
+        <v>0.3783081123004828</v>
       </c>
       <c r="Q37" t="n">
-        <v>3943.15639411599</v>
+        <v>0.384052741284836</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2521,46 +2527,46 @@
         <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>19.21089343106291</v>
+        <v>-18.41149987316928</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8386006665221544</v>
+        <v>3.486519678978993</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
       </c>
       <c r="G38" t="n">
-        <v>19.24148756668894</v>
+        <v>18.74133524059438</v>
       </c>
       <c r="H38" t="n">
-        <v>17.34171643341489</v>
+        <v>23.92148267546343</v>
       </c>
       <c r="I38" t="n">
-        <v>1.899771133274051</v>
+        <v>-5.180147434869045</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.538917375348187e-09</v>
+        <v>-5.101993842732215</v>
       </c>
       <c r="K38" t="n">
-        <v>17.34171642387597</v>
+        <v>18.81948883273121</v>
       </c>
       <c r="L38" t="n">
-        <v>3.933822174127531</v>
+        <v>50.83609959419667</v>
       </c>
       <c r="M38" t="n">
-        <v>1.020723897528121e-07</v>
+        <v>49.86030938165033</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9416853320885953</v>
+        <v>0.5242215085197082</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9578421063121413</v>
+        <v>-0.01096131940981237</v>
       </c>
       <c r="Q38" t="n">
-        <v>5946.304503469162</v>
+        <v>-0.01106805884857514</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2574,46 +2580,46 @@
         <v>37</v>
       </c>
       <c r="D39" t="n">
-        <v>-23.5748263108685</v>
+        <v>-1.146620732887129</v>
       </c>
       <c r="E39" t="n">
-        <v>-11.54109296391725</v>
+        <v>-11.9088671619944</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
       </c>
       <c r="G39" t="n">
-        <v>25.70302387727502</v>
+        <v>11.44439639271355</v>
       </c>
       <c r="H39" t="n">
-        <v>27.4828560166298</v>
+        <v>18.24881613206936</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.779832139354777</v>
+        <v>-6.804419739355811</v>
       </c>
       <c r="J39" t="n">
-        <v>3.82767082829047e-08</v>
+        <v>-5.756242486929398</v>
       </c>
       <c r="K39" t="n">
-        <v>27.48285605490651</v>
+        <v>12.49257364513996</v>
       </c>
       <c r="L39" t="n">
-        <v>3.933822174127537</v>
+        <v>39.51386202053212</v>
       </c>
       <c r="M39" t="n">
-        <v>1.020723959919228e-07</v>
+        <v>38.53807180798579</v>
       </c>
       <c r="N39" t="n">
-        <v>5.019789044320838</v>
+        <v>0.387996546628721</v>
       </c>
       <c r="O39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.8973703008144402</v>
+        <v>-0.1667477532243936</v>
       </c>
       <c r="Q39" t="n">
-        <v>-5570.894057347413</v>
+        <v>-0.1688455968444975</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2627,46 +2633,46 @@
         <v>38</v>
       </c>
       <c r="D40" t="n">
-        <v>-12.75215359731575</v>
+        <v>-37.50610043925393</v>
       </c>
       <c r="E40" t="n">
-        <v>25.83285277671557</v>
+        <v>-5.967553048644887</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
       </c>
       <c r="G40" t="n">
-        <v>28.96433826167509</v>
+        <v>39.52272910190202</v>
       </c>
       <c r="H40" t="n">
-        <v>28.95222697263694</v>
+        <v>30.19533498051533</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01211128903815251</v>
+        <v>9.327394121386689</v>
       </c>
       <c r="J40" t="n">
-        <v>2.920073334802417e-08</v>
+        <v>8.904123037002909</v>
       </c>
       <c r="K40" t="n">
-        <v>28.95222700183767</v>
+        <v>39.09945801751824</v>
       </c>
       <c r="L40" t="n">
-        <v>3.933822174127521</v>
+        <v>47.485144126544</v>
       </c>
       <c r="M40" t="n">
-        <v>1.020723798485646e-07</v>
+        <v>46.50935391399766</v>
       </c>
       <c r="N40" t="n">
-        <v>5.610674026812429</v>
+        <v>3.417240818027357</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.006106353745109185</v>
+        <v>0.06142422994150006</v>
       </c>
       <c r="Q40" t="n">
-        <v>37.90837790138469</v>
+        <v>0.06206524120613655</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2680,46 +2686,46 @@
         <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>-16.35321082151363</v>
+        <v>-26.41458011597199</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.056625987281194</v>
+        <v>0.7513546269754272</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
       </c>
       <c r="G41" t="n">
-        <v>16.89058784848077</v>
+        <v>27.41990981572093</v>
       </c>
       <c r="H41" t="n">
-        <v>15.45095281716993</v>
+        <v>26.55102935045411</v>
       </c>
       <c r="I41" t="n">
-        <v>1.439635031310836</v>
+        <v>0.8688804652668196</v>
       </c>
       <c r="J41" t="n">
-        <v>4.174754348447573e-08</v>
+        <v>0.1017942767296972</v>
       </c>
       <c r="K41" t="n">
-        <v>15.45095285891748</v>
+        <v>26.65282362718381</v>
       </c>
       <c r="L41" t="n">
-        <v>3.933822174127521</v>
+        <v>51.20844452037972</v>
       </c>
       <c r="M41" t="n">
-        <v>1.020723798291341e-07</v>
+        <v>50.23265430783339</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1813437734715652</v>
+        <v>1.593760335626616</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.7258469084240206</v>
+        <v>0.1071947143287212</v>
       </c>
       <c r="Q41" t="n">
-        <v>4506.073518545636</v>
+        <v>0.1082308576178076</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -2733,46 +2739,46 @@
         <v>40</v>
       </c>
       <c r="D42" t="n">
-        <v>26.06564217464059</v>
+        <v>19.35592066094645</v>
       </c>
       <c r="E42" t="n">
-        <v>3.156462640562879</v>
+        <v>-2.846144090792848</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>26.55830513266619</v>
+        <v>18.8781799218182</v>
       </c>
       <c r="H42" t="n">
-        <v>26.37700998418779</v>
+        <v>11.51236117780369</v>
       </c>
       <c r="I42" t="n">
-        <v>0.181295148478398</v>
+        <v>7.365818744014511</v>
       </c>
       <c r="J42" t="n">
-        <v>1.157329683159261e-08</v>
+        <v>8.451290457796716</v>
       </c>
       <c r="K42" t="n">
-        <v>26.37700999576109</v>
+        <v>19.96365163560041</v>
       </c>
       <c r="L42" t="n">
-        <v>3.933822174127544</v>
+        <v>33.25762742973014</v>
       </c>
       <c r="M42" t="n">
-        <v>1.020724016095386e-07</v>
+        <v>32.28183721718379</v>
       </c>
       <c r="N42" t="n">
-        <v>4.575090018073423</v>
+        <v>0.8329913020619781</v>
       </c>
       <c r="O42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.09140686048120863</v>
+        <v>-0.1882230813223421</v>
       </c>
       <c r="Q42" t="n">
-        <v>567.4557330244087</v>
+        <v>-0.1910466334308519</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -2786,46 +2792,46 @@
         <v>41</v>
       </c>
       <c r="D43" t="n">
-        <v>17.23406299489677</v>
+        <v>-22.86157206325889</v>
       </c>
       <c r="E43" t="n">
-        <v>-18.71534302127812</v>
+        <v>10.81971204616103</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
       </c>
       <c r="G43" t="n">
-        <v>24.10282033731087</v>
+        <v>25.80066422146151</v>
       </c>
       <c r="H43" t="n">
-        <v>24.58957162693866</v>
+        <v>25.38362877120477</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.4867512896277937</v>
+        <v>0.4170354502567406</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.684542014142987e-08</v>
+        <v>-0.4527235491005034</v>
       </c>
       <c r="K43" t="n">
-        <v>24.58957161009324</v>
+        <v>24.93090522210426</v>
       </c>
       <c r="L43" t="n">
-        <v>3.933822174127529</v>
+        <v>49.32951061221509</v>
       </c>
       <c r="M43" t="n">
-        <v>1.020723879474453e-07</v>
+        <v>48.35372039966875</v>
       </c>
       <c r="N43" t="n">
-        <v>3.856299095042059</v>
+        <v>1.382770890892334</v>
       </c>
       <c r="O43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.2454142258849361</v>
+        <v>0.1238356042468697</v>
       </c>
       <c r="Q43" t="n">
-        <v>-1523.536833350393</v>
+        <v>0.1250788799580303</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -2839,46 +2845,152 @@
         <v>42</v>
       </c>
       <c r="D44" t="n">
-        <v>-15.23674654061881</v>
+        <v>-13.11150102437511</v>
       </c>
       <c r="E44" t="n">
-        <v>-15.21640986076447</v>
+        <v>5.315349809221146</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
       </c>
       <c r="G44" t="n">
-        <v>23.04512706241528</v>
+        <v>14.1397278019014</v>
       </c>
       <c r="H44" t="n">
-        <v>20.25794479244911</v>
+        <v>22.18007887499116</v>
       </c>
       <c r="I44" t="n">
-        <v>2.78718226996617</v>
+        <v>-8.040351073089758</v>
       </c>
       <c r="J44" t="n">
-        <v>3.853256762779022e-08</v>
+        <v>-7.378399975623587</v>
       </c>
       <c r="K44" t="n">
-        <v>20.25794483098168</v>
+        <v>14.80167889936757</v>
       </c>
       <c r="L44" t="n">
-        <v>3.933822174127521</v>
+        <v>49.67156081365899</v>
       </c>
       <c r="M44" t="n">
-        <v>1.020723797826178e-07</v>
+        <v>48.69577060111265</v>
       </c>
       <c r="N44" t="n">
-        <v>2.114401843785655</v>
+        <v>0.02752295463717801</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.405264265294172</v>
+        <v>-0.09392301019214037</v>
       </c>
       <c r="Q44" t="n">
-        <v>8723.911365265883</v>
+        <v>-0.09485938072652304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="n">
+        <v>43</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-27.00195981101048</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-7.321362630038237</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="n">
+        <v>29.61851268237871</v>
+      </c>
+      <c r="H45" t="n">
+        <v>26.74402283261175</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.87448984976696</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.216993697016752</v>
+      </c>
+      <c r="K45" t="n">
+        <v>27.9610165296285</v>
+      </c>
+      <c r="L45" t="n">
+        <v>48.07243487330599</v>
+      </c>
+      <c r="M45" t="n">
+        <v>47.09664466075966</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.827082850623742</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.2390586535821486</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.2415224721178716</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-39.28688026501853</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-2.512193641921116</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="n">
+        <v>39.25887740899006</v>
+      </c>
+      <c r="H46" t="n">
+        <v>30.78044015598087</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8.478437253009194</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9.888102442041388</v>
+      </c>
+      <c r="K46" t="n">
+        <v>40.66854259802226</v>
+      </c>
+      <c r="L46" t="n">
+        <v>48.53930501196299</v>
+      </c>
+      <c r="M46" t="n">
+        <v>47.56351479941665</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.601762533068822</v>
+      </c>
+      <c r="O46" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-0.2023341542053397</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>-0.2043991121904097</v>
       </c>
     </row>
   </sheetData>
